--- a/public/documents/pieces-defense/Consommation-personnel-et-offerts.xlsx
+++ b/public/documents/pieces-defense/Consommation-personnel-et-offerts.xlsx
@@ -624,7 +624,7 @@
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>44 L = disparu Picon entier</t>
+          <t>~1,7 Picon Biere/j x 4 cl de Picon x 662 j (≈44 L)</t>
         </is>
       </c>
     </row>
@@ -812,7 +812,7 @@
         </is>
       </c>
       <c r="B3" s="6" t="n">
-        <v>10657</v>
+        <v>10622</v>
       </c>
     </row>
     <row r="4">
@@ -828,7 +828,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>- Vendu en cocktails (caisse)</t>
+          <t>- Vendu en cocktails (caisse, biere des cocktails incluse)</t>
         </is>
       </c>
       <c r="B5" s="4" t="n">
@@ -897,17 +897,17 @@
     </row>
     <row r="12">
       <c r="A12" s="5">
-        <f> PERTE REELLE RESIDUELLE (23.0 % des achats)</f>
+        <f> PERTE REELLE RESIDUELLE (22.8 % des achats)</f>
         <v/>
       </c>
       <c r="B12" s="6" t="n">
-        <v>2454</v>
+        <v>2419</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Perte d'exploitation normale d'un bar (casse, evaporation, mousse, sur-versement non mesure). La jurisprudence CHR admet 22-25 %. AUCUNE vente au noir : CA bancarise, especes 1,3 %.</t>
+          <t>Perte d'exploitation d'un bar (casse, evaporation, mousse, sur-versement non mesure). A rapprocher de l'abattement que l'administration retient elle-meme en reconstitution de bar (CAA Paris, 17 mars 2021 : 22 % des achats pour personnel/offerts/pertes/vol, methode validee ; n de requete a fiabiliser). AUCUNE vente au noir : CA bancarise, especes 1,3 %.</t>
         </is>
       </c>
     </row>

--- a/public/documents/pieces-defense/Consommation-personnel-et-offerts.xlsx
+++ b/public/documents/pieces-defense/Consommation-personnel-et-offerts.xlsx
@@ -779,7 +779,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:B17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -878,36 +878,66 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>- Sur-versement au verre (~8 %)</t>
+          <t>- Sur-versement au verre et cocktails (free-pour, Kerr 2008)</t>
         </is>
       </c>
       <c r="B10" s="4" t="n">
-        <v>446</v>
+        <v>807</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
+          <t>- Degustation offerte (pichet + vin nomme au verre)</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="n">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>- Cremant jete en fin de journee (eventé)</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="n">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>- Freinte technique de la biere pression (mousse, lignes)</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="n">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
           <t>- Stock final (inventaire)</t>
         </is>
       </c>
-      <c r="B11" s="4" t="n">
+      <c r="B14" s="4" t="n">
         <v>213</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="5">
-        <f> PERTE REELLE RESIDUELLE (22.8 % des achats)</f>
+    <row r="15">
+      <c r="A15" s="5">
+        <f> PERTE REELLE RESIDUELLE (15.9 % des achats)</f>
         <v/>
       </c>
-      <c r="B12" s="6" t="n">
-        <v>2419</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Perte d'exploitation d'un bar (casse, evaporation, mousse, sur-versement non mesure). A rapprocher de l'abattement que l'administration retient elle-meme en reconstitution de bar (CAA Paris, 17 mars 2021 : 22 % des achats pour personnel/offerts/pertes/vol, methode validee ; n de requete a fiabiliser). AUCUNE vente au noir : CA bancarise, especes 1,3 %.</t>
+      <c r="B15" s="6" t="n">
+        <v>1690</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Le residuel est desormais la seule perte IRREDUCTIBLE (casse, evaporation, fonds de verre, rincage) : les autres pertes sont chiffrees en postes explicites. La perte d'exploitation TOTALE (conso personnel + offerts + sur-versement + degustation + cremant + freinte + casse) atteint 28.7 % des achats, AU-DESSUS des 22 % que l'administration retient elle-meme en reconstitution de bar (CAA Paris, 17 mars 2021, methode validee ; n de requete a fiabiliser). AUCUNE vente au noir : CA bancarise, especes 1,3 %.</t>
         </is>
       </c>
     </row>

--- a/public/documents/pieces-defense/Consommation-personnel-et-offerts.xlsx
+++ b/public/documents/pieces-defense/Consommation-personnel-et-offerts.xlsx
@@ -779,7 +779,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B17"/>
+  <dimension ref="A1:B18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -878,21 +878,21 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>- Sur-versement au verre et cocktails (free-pour, Kerr 2008)</t>
+          <t>- Sur-versement vins/spiritueux/cocktails (free-pour : Kerr 2008, Wansink 2005)</t>
         </is>
       </c>
       <c r="B10" s="4" t="n">
-        <v>807</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>- Degustation offerte (pichet + vin nomme au verre)</t>
+          <t>- Degustation offerte (note par note, annexe C)</t>
         </is>
       </c>
       <c r="B11" s="4" t="n">
-        <v>113</v>
+        <v>126</v>
       </c>
     </row>
     <row r="12">
@@ -902,40 +902,50 @@
         </is>
       </c>
       <c r="B12" s="4" t="n">
-        <v>126</v>
+        <v>260</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>- Freinte technique de la biere pression (mousse, lignes)</t>
+          <t>- Cremant sur-versé (free-pour +23,6 %)</t>
         </is>
       </c>
       <c r="B13" s="4" t="n">
-        <v>129</v>
+        <v>87</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
+          <t>- Freinte technique de la biere pression (mousse, lignes)</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="n">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
           <t>- Stock final (inventaire)</t>
         </is>
       </c>
-      <c r="B14" s="4" t="n">
+      <c r="B15" s="4" t="n">
         <v>213</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="5">
-        <f> PERTE REELLE RESIDUELLE (15.9 % des achats)</f>
+    <row r="16">
+      <c r="A16" s="5">
+        <f> PERTE REELLE RESIDUELLE (11.4 % des achats)</f>
         <v/>
       </c>
-      <c r="B15" s="6" t="n">
-        <v>1690</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
+      <c r="B16" s="6" t="n">
+        <v>1207</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
         <is>
           <t>Le residuel est desormais la seule perte IRREDUCTIBLE (casse, evaporation, fonds de verre, rincage) : les autres pertes sont chiffrees en postes explicites. La perte d'exploitation TOTALE (conso personnel + offerts + sur-versement + degustation + cremant + freinte + casse) atteint 28.7 % des achats, AU-DESSUS des 22 % que l'administration retient elle-meme en reconstitution de bar (CAA Paris, 17 mars 2021, methode validee ; n de requete a fiabiliser). AUCUNE vente au noir : CA bancarise, especes 1,3 %.</t>
         </is>

--- a/public/documents/pieces-defense/Consommation-personnel-et-offerts.xlsx
+++ b/public/documents/pieces-defense/Consommation-personnel-et-offerts.xlsx
@@ -882,7 +882,7 @@
         </is>
       </c>
       <c r="B10" s="4" t="n">
-        <v>1056</v>
+        <v>1058</v>
       </c>
     </row>
     <row r="11">
@@ -937,11 +937,11 @@
     </row>
     <row r="16">
       <c r="A16" s="5">
-        <f> PERTE REELLE RESIDUELLE (11.4 % des achats)</f>
+        <f> PERTE REELLE RESIDUELLE (11.3 % des achats)</f>
         <v/>
       </c>
       <c r="B16" s="6" t="n">
-        <v>1207</v>
+        <v>1205</v>
       </c>
     </row>
     <row r="18">

--- a/public/documents/pieces-defense/Consommation-personnel-et-offerts.xlsx
+++ b/public/documents/pieces-defense/Consommation-personnel-et-offerts.xlsx
@@ -882,7 +882,7 @@
         </is>
       </c>
       <c r="B10" s="4" t="n">
-        <v>1058</v>
+        <v>720</v>
       </c>
     </row>
     <row r="11">
@@ -937,11 +937,11 @@
     </row>
     <row r="16">
       <c r="A16" s="5">
-        <f> PERTE REELLE RESIDUELLE (11.3 % des achats)</f>
+        <f> PERTE REELLE RESIDUELLE (14.5 % des achats)</f>
         <v/>
       </c>
       <c r="B16" s="6" t="n">
-        <v>1205</v>
+        <v>1543</v>
       </c>
     </row>
     <row r="18">
